--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/entropy/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/entropy/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -688,6 +688,265 @@
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=10.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.8,scale_th=10.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>96.34</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.7,scale_th=10.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>83.01000000000001</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>90.93000000000001</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=10.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.6,scale_th=10.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.7,scale_th=2.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.7,scale_th=3.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>96.34</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.7,scale_th=5.0,type=entropy</t>
         </is>
       </c>
     </row>
